--- a/entrega-1/05-reporte-de-ejecucion.xlsx
+++ b/entrega-1/05-reporte-de-ejecucion.xlsx
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,11 +104,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1299,14 +1291,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>DEF-017</t>
+          <t>DEF-017 (corregido)</t>
         </is>
       </c>
     </row>
@@ -1336,14 +1328,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>DEF-017</t>
+          <t>DEF-017 (corregido)</t>
         </is>
       </c>
     </row>
@@ -1373,14 +1365,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>DEF-017</t>
+          <t>DEF-017 (corregido)</t>
         </is>
       </c>
     </row>
@@ -1410,14 +1402,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>DEF-017</t>
+          <t>DEF-017 (corregido)</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1439,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>DEF-017</t>
+          <t>DEF-017 (corregido)</t>
         </is>
       </c>
     </row>
@@ -3018,14 +3010,14 @@
       <c r="G76" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Resumen</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>Planificados</t>
         </is>
@@ -3035,47 +3027,47 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>Ejecutados</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>No ejecutados</t>
         </is>
@@ -3085,58 +3077,58 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>% avance (ejecutados/planificados)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>95 %</t>
+          <t>100 %</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>% aprobados sobre ejecutados</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>96 %</t>
+          <t>97 %</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Por módulo</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Casos</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -3171,13 +3163,13 @@
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
